--- a/data/trans_dic/IP11C$urgencias-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$urgencias-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y acudieron a un servicio de urgencias</t>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y acudieron a un servicio de urgencias (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,2; 84,85</t>
+          <t>14,94; 85,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,21; 59,47</t>
+          <t>16,7; 59,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -736,12 +737,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,94; 83,23</t>
+          <t>27,67; 83,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,64; 93,04</t>
+          <t>50,11; 93,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -756,17 +757,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,55; 77,81</t>
+          <t>26,56; 76,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37,98; 73,8</t>
+          <t>37,88; 72,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,17; 100,0</t>
+          <t>18,71; 100,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,69; 80,91</t>
+          <t>40,86; 81,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,2; 64,26</t>
+          <t>25,74; 64,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66,06; 100,0</t>
+          <t>66,88; 100,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,69; 88,78</t>
+          <t>12,47; 87,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,82; 71,77</t>
+          <t>34,32; 70,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,12; 56,18</t>
+          <t>25,05; 55,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,25; 93,36</t>
+          <t>47,01; 91,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>76,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41,15; 71,74</t>
+          <t>41,04; 70,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30,69; 54,92</t>
+          <t>29,91; 54,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61,19; 92,72</t>
+          <t>61,66; 93,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>51,59; 95,38</t>
+          <t>51,76; 95,46</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38,59; 91,18</t>
+          <t>38,45; 92,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,6; 80,31</t>
+          <t>31,26; 80,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49,6; 100,0</t>
+          <t>60,26; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40,25; 100,0</t>
+          <t>30,9; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,01; 87,63</t>
+          <t>42,74; 87,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,67; 85,16</t>
+          <t>36,15; 85,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,32; 89,0</t>
+          <t>42,41; 88,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,6; 100,0</t>
+          <t>24,94; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49,23; 84,13</t>
+          <t>46,67; 83,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43,04; 78,6</t>
+          <t>42,85; 77,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>56,21; 89,3</t>
+          <t>56,15; 90,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39,32; 93,65</t>
+          <t>43,99; 94,19</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,1; 81,04</t>
+          <t>29,04; 79,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,18; 82,99</t>
+          <t>35,93; 82,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,65; 100,0</t>
+          <t>56,05; 100,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,44; 92,08</t>
+          <t>35,61; 92,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>54,71; 94,53</t>
+          <t>54,54; 94,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,65; 79,42</t>
+          <t>47,17; 80,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,5; 94,84</t>
+          <t>61,53; 94,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59,16; 100,0</t>
+          <t>56,07; 100,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50,94; 81,63</t>
+          <t>49,93; 81,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49,74; 76,41</t>
+          <t>50,45; 76,47</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66,95; 93,62</t>
+          <t>68,38; 93,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,91; 93,64</t>
+          <t>56,71; 92,92</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>47,21; 71,98</t>
+          <t>47,98; 73,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,36; 60,95</t>
+          <t>39,11; 61,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74,54; 97,15</t>
+          <t>76,05; 97,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46,66; 84,29</t>
+          <t>45,78; 84,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>51,93; 74,21</t>
+          <t>52,25; 74,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,34; 66,11</t>
+          <t>47,12; 65,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,69; 84,75</t>
+          <t>61,57; 84,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>62,43; 93,92</t>
+          <t>61,6; 93,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>53,35; 70,34</t>
+          <t>52,56; 69,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45,56; 60,72</t>
+          <t>46,07; 60,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69,61; 86,64</t>
+          <t>71,28; 87,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,36; 85,54</t>
+          <t>62,85; 87,22</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y acudieron a un servicio de urgencias (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1716</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3795</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4038</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7224</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1456</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5753</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11019</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2575</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1058</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>527; 3018</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1789; 6374</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 758</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1947; 5885</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4615; 8580</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2739</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1337</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2806; 8117</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>7547; 14389</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>722; 3858</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2095</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>8247</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8234</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5867</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1883</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8411</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>11496</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8405</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5558</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>16658</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>19730</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>14272</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>7441</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>5461; 10873</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4754; 11910</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4244; 6346</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>464; 3251</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>5512; 11348</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7075; 15601</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>5350; 10392</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>12076; 20696</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>13972; 25541</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>10929; 16532</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>4802; 8855</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6017</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6289</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5648</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4149</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>7598</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7901</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>8490</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>13615</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>14138</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>9412</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3381; 8153</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3369; 8727</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3776; 6265</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1507; 4878</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4727; 9709</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4503; 10619</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5170; 10798</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1921; 7702</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>9265; 16603</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>9955; 18051</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>10362; 16611</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5534; 11850</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5428</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7084</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8256</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5336</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>9580</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>15151</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>12041</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>8197</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>15008</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>22236</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>20297</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>13533</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2793; 7618</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4223; 9731</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5402; 9639</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2777; 7197</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>6746; 11683</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>11072; 18902</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>8869; 13668</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>5290; 9436</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>10978; 17823</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>17771; 26938</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>16449; 22597</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>9773; 16013</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>21408</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>25402</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20890</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11718</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>29626</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>41772</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>30392</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>19726</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>51034</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>67174</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>51282</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>31444</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>16940; 26030</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>20223; 31799</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>17772; 22752</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7852; 14574</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>24310; 34737</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>34579; 48331</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>25073; 34505</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>14805; 22556</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>43009; 57257</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>57634; 76231</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>45684; 56366</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>25883; 35922</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11C$urgencias-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$urgencias-Edad-trans_dic.xlsx
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,94; 85,51</t>
+          <t>14,74; 84,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,7; 59,51</t>
+          <t>17,05; 60,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,67; 83,62</t>
+          <t>28,25; 83,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,11; 93,16</t>
+          <t>55,04; 93,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,56; 76,83</t>
+          <t>30,61; 79,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37,88; 72,23</t>
+          <t>36,78; 73,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -857,37 +857,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,86; 81,36</t>
+          <t>37,97; 80,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,74; 64,48</t>
+          <t>25,88; 63,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66,88; 100,0</t>
+          <t>65,96; 100,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,47; 87,44</t>
+          <t>12,88; 88,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,32; 70,66</t>
+          <t>31,8; 72,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,05; 55,25</t>
+          <t>24,43; 56,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,01; 91,32</t>
+          <t>47,84; 91,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,22 +897,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41,04; 70,34</t>
+          <t>42,22; 71,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,91; 54,68</t>
+          <t>30,58; 55,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61,66; 93,28</t>
+          <t>59,94; 92,87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>51,76; 95,46</t>
+          <t>52,15; 95,57</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38,45; 92,71</t>
+          <t>39,82; 91,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,26; 80,98</t>
+          <t>31,07; 80,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60,26; 100,0</t>
+          <t>57,83; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,9; 100,0</t>
+          <t>35,69; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42,74; 87,78</t>
+          <t>43,37; 92,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,15; 85,24</t>
+          <t>35,55; 82,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,41; 88,57</t>
+          <t>44,27; 88,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,94; 100,0</t>
+          <t>22,62; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46,67; 83,62</t>
+          <t>50,54; 84,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42,85; 77,69</t>
+          <t>43,59; 78,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>56,15; 90,0</t>
+          <t>58,96; 91,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43,99; 94,19</t>
+          <t>44,77; 93,93</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,04; 79,2</t>
+          <t>27,76; 80,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,93; 82,79</t>
+          <t>36,57; 82,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,05; 100,0</t>
+          <t>58,47; 100,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,61; 92,3</t>
+          <t>31,26; 92,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>54,54; 94,46</t>
+          <t>51,3; 89,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,17; 80,53</t>
+          <t>47,72; 80,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,53; 94,82</t>
+          <t>61,08; 94,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>56,07; 100,0</t>
+          <t>53,9; 100,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49,93; 81,06</t>
+          <t>49,24; 83,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50,45; 76,47</t>
+          <t>50,07; 76,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68,38; 93,94</t>
+          <t>68,91; 93,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>56,71; 92,92</t>
+          <t>53,25; 92,32</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>47,98; 73,73</t>
+          <t>46,15; 72,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39,11; 61,49</t>
+          <t>36,98; 60,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76,05; 97,36</t>
+          <t>73,31; 96,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45,78; 84,98</t>
+          <t>47,07; 85,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>52,25; 74,66</t>
+          <t>52,74; 74,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,12; 65,87</t>
+          <t>47,51; 66,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,57; 84,73</t>
+          <t>61,89; 84,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>61,6; 93,85</t>
+          <t>63,09; 93,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>52,56; 69,97</t>
+          <t>53,37; 70,18</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46,07; 60,94</t>
+          <t>46,54; 60,79</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71,28; 87,94</t>
+          <t>70,74; 87,58</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,85; 87,22</t>
+          <t>62,85; 87,16</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>527; 3018</t>
+          <t>520; 2994</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1789; 6374</t>
+          <t>1826; 6488</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1947; 5885</t>
+          <t>1988; 5898</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4615; 8580</t>
+          <t>5069; 8568</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2806; 8117</t>
+          <t>3234; 8347</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7547; 14389</t>
+          <t>7328; 14572</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1853,37 +1853,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5461; 10873</t>
+          <t>5074; 10810</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4754; 11910</t>
+          <t>4780; 11777</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4244; 6346</t>
+          <t>4186; 6346</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>464; 3251</t>
+          <t>479; 3301</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5512; 11348</t>
+          <t>5107; 11694</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7075; 15601</t>
+          <t>6899; 15855</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5350; 10392</t>
+          <t>5444; 10429</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1893,22 +1893,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12076; 20696</t>
+          <t>12424; 21020</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13972; 25541</t>
+          <t>14283; 26007</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10929; 16532</t>
+          <t>10624; 16460</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4802; 8855</t>
+          <t>4837; 8865</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3381; 8153</t>
+          <t>3502; 8017</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3369; 8727</t>
+          <t>3349; 8710</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3776; 6265</t>
+          <t>3623; 6265</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1507; 4878</t>
+          <t>1741; 4878</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4727; 9709</t>
+          <t>4797; 10241</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4503; 10619</t>
+          <t>4428; 10310</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5170; 10798</t>
+          <t>5397; 10801</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1921; 7702</t>
+          <t>1742; 7702</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9265; 16603</t>
+          <t>10034; 16865</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9955; 18051</t>
+          <t>10127; 18195</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10362; 16611</t>
+          <t>10881; 16813</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5534; 11850</t>
+          <t>5632; 11817</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2793; 7618</t>
+          <t>2670; 7703</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4223; 9731</t>
+          <t>4299; 9725</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5402; 9639</t>
+          <t>5636; 9639</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2777; 7197</t>
+          <t>2437; 7190</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6746; 11683</t>
+          <t>6345; 11090</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11072; 18902</t>
+          <t>11202; 18791</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8869; 13668</t>
+          <t>8804; 13665</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5290; 9436</t>
+          <t>5086; 9436</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10978; 17823</t>
+          <t>10827; 18333</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17771; 26938</t>
+          <t>17636; 27055</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16449; 22597</t>
+          <t>16576; 22578</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9773; 16013</t>
+          <t>9176; 15909</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16940; 26030</t>
+          <t>16294; 25613</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20223; 31799</t>
+          <t>19123; 31080</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17772; 22752</t>
+          <t>17133; 22651</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7852; 14574</t>
+          <t>8073; 14610</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24310; 34737</t>
+          <t>24536; 34588</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34579; 48331</t>
+          <t>34859; 48560</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25073; 34505</t>
+          <t>25204; 34525</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14805; 22556</t>
+          <t>15164; 22468</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43009; 57257</t>
+          <t>43669; 57426</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>57634; 76231</t>
+          <t>58216; 76037</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45684; 56366</t>
+          <t>45339; 56135</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25883; 35922</t>
+          <t>25886; 35896</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11C$urgencias-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$urgencias-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>57,38%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>78,44%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>53,14%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>47,44%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>48,64%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>35,43%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>46,2%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>57,38%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>78,44%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>53,14%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>46,83%</t>
         </is>
       </c>
     </row>
@@ -717,57 +717,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,74; 84,84</t>
+          <t>20,94; 83,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,05; 60,57</t>
+          <t>45,64; 93,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 100,0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 100,0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14,2; 84,85</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12,21; 59,47</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>28,25; 83,81</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>55,04; 93,03</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,61; 79,01</t>
+          <t>30,55; 77,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,78; 73,14</t>
+          <t>37,98; 73,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,71; 100,0</t>
+          <t>18,17; 100,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>52,37%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>40,71%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>73,87%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>61,71%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>44,58%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>92,45%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>50,64%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>52,37%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>40,71%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>73,87%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>77,71%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>37,97; 80,9</t>
+          <t>30,82; 71,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,88; 63,76</t>
+          <t>25,12; 56,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65,96; 100,0</t>
+          <t>44,25; 93,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,88; 88,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,8; 72,81</t>
+          <t>36,69; 80,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,43; 56,15</t>
+          <t>26,2; 64,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,84; 91,65</t>
+          <t>66,06; 100,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,93; 89,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42,22; 71,44</t>
+          <t>41,15; 71,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30,58; 55,68</t>
+          <t>30,69; 54,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59,94; 92,87</t>
+          <t>61,19; 92,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,15; 95,57</t>
+          <t>47,44; 95,35</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>68,7%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>63,42%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>69,64%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>66,99%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>68,42%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>58,35%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>90,15%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>85,05%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>68,7%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>63,42%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,64%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,68%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,82; 91,17</t>
+          <t>40,01; 87,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,07; 80,82</t>
+          <t>38,67; 85,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,83; 100,0</t>
+          <t>42,32; 89,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35,69; 100,0</t>
+          <t>24,17; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43,37; 92,6</t>
+          <t>38,59; 91,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,55; 82,76</t>
+          <t>29,6; 80,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,27; 88,6</t>
+          <t>49,6; 100,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,62; 100,0</t>
+          <t>41,84; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50,54; 84,94</t>
+          <t>49,23; 84,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43,59; 78,31</t>
+          <t>43,04; 78,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58,96; 91,1</t>
+          <t>56,21; 89,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44,77; 93,93</t>
+          <t>38,31; 94,0</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>77,45%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>64,55%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>83,53%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>87,57%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>56,44%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>60,27%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>85,65%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>68,44%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>77,45%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>64,55%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>83,53%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>79,1%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,76; 80,09</t>
+          <t>54,71; 94,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,57; 82,74</t>
+          <t>48,65; 79,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58,47; 100,0</t>
+          <t>62,5; 94,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,26; 92,21</t>
+          <t>59,75; 100,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,3; 89,66</t>
+          <t>28,1; 81,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,72; 80,06</t>
+          <t>36,18; 82,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,08; 94,79</t>
+          <t>56,65; 100,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>53,9; 100,0</t>
+          <t>35,02; 92,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49,24; 83,38</t>
+          <t>50,94; 81,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50,07; 76,8</t>
+          <t>49,74; 76,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68,91; 93,86</t>
+          <t>66,95; 93,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53,25; 92,32</t>
+          <t>57,91; 93,88</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>63,68%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56,93%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>74,63%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>81,09%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>60,64%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>49,12%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>89,39%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>68,32%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>63,68%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>74,63%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>75,97%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>46,15; 72,55</t>
+          <t>51,93; 74,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36,98; 60,1</t>
+          <t>46,34; 66,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,31; 96,93</t>
+          <t>61,69; 84,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47,07; 85,19</t>
+          <t>60,56; 93,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>52,74; 74,34</t>
+          <t>47,21; 71,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,51; 66,18</t>
+          <t>38,36; 60,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,89; 84,78</t>
+          <t>74,54; 97,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>63,09; 93,49</t>
+          <t>48,84; 85,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>53,37; 70,18</t>
+          <t>53,35; 70,34</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46,54; 60,79</t>
+          <t>45,56; 60,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70,74; 87,58</t>
+          <t>69,61; 86,64</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,85; 87,16</t>
+          <t>61,46; 85,56</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,32 +1509,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4038</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7224</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1456</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1716</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>3795</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1119</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4038</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7224</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1456</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>258</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>823</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>520; 2994</t>
+          <t>1474; 5857</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1826; 6488</t>
+          <t>4203; 8569</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>0; 2739</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1191</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>501; 2994</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1308; 6370</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0; 758</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1988; 5898</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5069; 8568</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2739</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1337</t>
+          <t>0; 566</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3234; 8347</t>
+          <t>3228; 8221</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7328; 14572</t>
+          <t>7567; 14702</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>722; 3858</t>
+          <t>701; 3858</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2095</t>
+          <t>0; 1757</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8411</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11496</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8405</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4702</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>8247</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>8234</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>5867</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1883</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8411</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11496</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8405</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7441</t>
+          <t>6472</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5074; 10810</t>
+          <t>4949; 11526</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4780; 11777</t>
+          <t>7093; 15865</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4186; 6346</t>
+          <t>5035; 10623</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>479; 3301</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5107; 11694</t>
+          <t>4904; 10812</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6899; 15855</t>
+          <t>4838; 11869</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5444; 10429</t>
+          <t>4192; 6346</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>360; 3252</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12424; 21020</t>
+          <t>12109; 21107</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14283; 26007</t>
+          <t>14333; 25652</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10624; 16460</t>
+          <t>10846; 16433</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4837; 8865</t>
+          <t>3952; 7942</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7598</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7901</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8490</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5039</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>6017</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>6289</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>5648</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4149</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>7598</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7901</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>8490</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9294</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3502; 8017</t>
+          <t>4425; 9692</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3349; 8710</t>
+          <t>4818; 10610</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3623; 6265</t>
+          <t>5159; 10849</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1741; 4878</t>
+          <t>1818; 7522</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4797; 10241</t>
+          <t>3394; 8019</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4428; 10310</t>
+          <t>3190; 8655</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5397; 10801</t>
+          <t>3107; 6265</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1742; 7702</t>
+          <t>2059; 4922</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10034; 16865</t>
+          <t>9774; 16703</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10127; 18195</t>
+          <t>9999; 18262</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10881; 16813</t>
+          <t>10375; 16481</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5632; 11817</t>
+          <t>4767; 11697</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9580</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15151</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12041</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7737</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>5428</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>7084</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>8256</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5336</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9580</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15151</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12041</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13533</t>
+          <t>13371</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2670; 7703</t>
+          <t>6766; 11693</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4299; 9725</t>
+          <t>11420; 18641</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5636; 9639</t>
+          <t>9009; 13671</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2437; 7190</t>
+          <t>5280; 8836</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6345; 11090</t>
+          <t>2702; 7795</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11202; 18791</t>
+          <t>4253; 9754</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8804; 13665</t>
+          <t>5460; 9639</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5086; 9436</t>
+          <t>2826; 7459</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10827; 18333</t>
+          <t>11199; 17947</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17636; 27055</t>
+          <t>17522; 26915</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16576; 22578</t>
+          <t>16104; 22518</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9176; 15909</t>
+          <t>9789; 15870</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>29626</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>41772</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>30392</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>18044</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>21408</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>25402</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>20890</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>11718</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>29626</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>41772</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>30392</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19726</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31444</t>
+          <t>29960</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16294; 25613</t>
+          <t>24159; 34526</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19123; 31080</t>
+          <t>34003; 48513</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17133; 22651</t>
+          <t>25123; 34515</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8073; 14610</t>
+          <t>13475; 20795</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24536; 34588</t>
+          <t>16668; 25410</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34859; 48560</t>
+          <t>19839; 31517</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25204; 34525</t>
+          <t>17420; 22702</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15164; 22468</t>
+          <t>8392; 14651</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43669; 57426</t>
+          <t>43659; 57555</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58216; 76037</t>
+          <t>56997; 75948</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45339; 56135</t>
+          <t>44615; 55531</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25886; 35896</t>
+          <t>24237; 33742</t>
         </is>
       </c>
     </row>
